--- a/Songs.xlsx
+++ b/Songs.xlsx
@@ -158,7 +158,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -181,10 +181,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -380,15 +376,15 @@
       <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G2" s="3" t="str">
-        <f aca="false">"""C:/Users/t/Desktop/Music/ffmpeg-master-latest-win64-gpl/bin/ffmpeg.exe"" -i ""C:/Users/t/Desktop/Music/Downloaded/"&amp;SUBSTITUTE(E2,"https://www.youtube.com/watch?v=","")&amp;".opus"" -metadata title="""&amp;D2&amp;""" -metadata artist="""&amp;C2&amp;""" -metadata album="""&amp;IF(ISBLANK(B2), "-", B2)&amp;""" -metadata genre="""&amp;A2&amp;""" -codec copy ""C:/Users/t/Desktop/Music/Completed/"&amp;SUBSTITUTE(E2,"https://www.youtube.com/watch?v=","")&amp;".opus"""</f>
-        <v>"C:/Users/t/Desktop/Music/ffmpeg-master-latest-win64-gpl/bin/ffmpeg.exe" -i "C:/Users/t/Desktop/Music/Downloaded/TW9d8vYrVFQ.opus" -metadata title="Sky High" -metadata artist="Elektronomia" -metadata album="NoCopyrightSounds" -metadata genre="Instrumental" -codec copy "C:/Users/t/Desktop/Music/Completed/TW9d8vYrVFQ.opus"</v>
+        <f aca="false">"""ffmpeg-master-latest-win64-gpl/bin/ffmpeg.exe"" -i ""Downloaded/"&amp;SUBSTITUTE(E2,"https://www.youtube.com/watch?v=","")&amp;".opus"" -metadata title="""&amp;D2&amp;""" -metadata artist="""&amp;C2&amp;""" -metadata album="""&amp;IF(ISBLANK(B2), "-", B2)&amp;""" -metadata genre="""&amp;A2&amp;""" -codec copy ""Completed/"&amp;SUBSTITUTE(E2,"https://www.youtube.com/watch?v=","")&amp;".opus"""</f>
+        <v>"ffmpeg-master-latest-win64-gpl/bin/ffmpeg.exe" -i "Downloaded/TW9d8vYrVFQ.opus" -metadata title="Sky High" -metadata artist="Elektronomia" -metadata album="NoCopyrightSounds" -metadata genre="Instrumental" -codec copy "Completed/TW9d8vYrVFQ.opus"</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -401,7 +397,7 @@
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -411,8 +407,8 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="str">
-        <f aca="false">"""C:/Users/t/Desktop/Music/ffmpeg-master-latest-win64-gpl/bin/ffmpeg.exe"" -i ""C:/Users/t/Desktop/Music/Downloaded/"&amp;SUBSTITUTE(E3,"https://www.youtube.com/watch?v=","")&amp;".opus"" -metadata title="""&amp;D3&amp;""" -metadata artist="""&amp;C3&amp;""" -metadata album="""&amp;IF(ISBLANK(B3), "-", B3)&amp;""" -metadata genre="""&amp;A3&amp;""" -codec copy ""C:/Users/t/Desktop/Music/Completed/"&amp;SUBSTITUTE(E3,"https://www.youtube.com/watch?v=","")&amp;".opus"""</f>
-        <v>"C:/Users/t/Desktop/Music/ffmpeg-master-latest-win64-gpl/bin/ffmpeg.exe" -i "C:/Users/t/Desktop/Music/Downloaded/fzNMd3Tu1Zw.opus" -metadata title="Energy" -metadata artist="Elektronomia" -metadata album="NoCopyrightSounds" -metadata genre="Instrumental" -codec copy "C:/Users/t/Desktop/Music/Completed/fzNMd3Tu1Zw.opus"</v>
+        <f aca="false">"""ffmpeg-master-latest-win64-gpl/bin/ffmpeg.exe"" -i ""Downloaded/"&amp;SUBSTITUTE(E3,"https://www.youtube.com/watch?v=","")&amp;".opus"" -metadata title="""&amp;D3&amp;""" -metadata artist="""&amp;C3&amp;""" -metadata album="""&amp;IF(ISBLANK(B3), "-", B3)&amp;""" -metadata genre="""&amp;A3&amp;""" -codec copy ""Completed/"&amp;SUBSTITUTE(E3,"https://www.youtube.com/watch?v=","")&amp;".opus"""</f>
+        <v>"ffmpeg-master-latest-win64-gpl/bin/ffmpeg.exe" -i "Downloaded/fzNMd3Tu1Zw.opus" -metadata title="Energy" -metadata artist="Elektronomia" -metadata album="NoCopyrightSounds" -metadata genre="Instrumental" -codec copy "Completed/fzNMd3Tu1Zw.opus"</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -435,8 +431,8 @@
         <v>12</v>
       </c>
       <c r="G4" s="3" t="str">
-        <f aca="false">"""C:/Users/t/Desktop/Music/ffmpeg-master-latest-win64-gpl/bin/ffmpeg.exe"" -i ""C:/Users/t/Desktop/Music/Downloaded/"&amp;SUBSTITUTE(E4,"https://www.youtube.com/watch?v=","")&amp;".opus"" -metadata title="""&amp;D4&amp;""" -metadata artist="""&amp;C4&amp;""" -metadata album="""&amp;IF(ISBLANK(B4), "-", B4)&amp;""" -metadata genre="""&amp;A4&amp;""" -codec copy ""C:/Users/t/Desktop/Music/Completed/"&amp;SUBSTITUTE(E4,"https://www.youtube.com/watch?v=","")&amp;".opus"""</f>
-        <v>"C:/Users/t/Desktop/Music/ffmpeg-master-latest-win64-gpl/bin/ffmpeg.exe" -i "C:/Users/t/Desktop/Music/Downloaded/jK2aIUmmdP4.opus" -metadata title="My Heart" -metadata artist="Different Heaven, EH!DE" -metadata album="NoCopyrightSounds" -metadata genre="Instrumental" -codec copy "C:/Users/t/Desktop/Music/Completed/jK2aIUmmdP4.opus"</v>
+        <f aca="false">"""ffmpeg-master-latest-win64-gpl/bin/ffmpeg.exe"" -i ""Downloaded/"&amp;SUBSTITUTE(E4,"https://www.youtube.com/watch?v=","")&amp;".opus"" -metadata title="""&amp;D4&amp;""" -metadata artist="""&amp;C4&amp;""" -metadata album="""&amp;IF(ISBLANK(B4), "-", B4)&amp;""" -metadata genre="""&amp;A4&amp;""" -codec copy ""Completed/"&amp;SUBSTITUTE(E4,"https://www.youtube.com/watch?v=","")&amp;".opus"""</f>
+        <v>"ffmpeg-master-latest-win64-gpl/bin/ffmpeg.exe" -i "Downloaded/jK2aIUmmdP4.opus" -metadata title="My Heart" -metadata artist="Different Heaven, EH!DE" -metadata album="NoCopyrightSounds" -metadata genre="Instrumental" -codec copy "Completed/jK2aIUmmdP4.opus"</v>
       </c>
     </row>
   </sheetData>
